--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487877_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487877_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0582</v>
+        <v>4.4529</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7642</v>
+        <v>3.1625</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.706</v>
+        <v>1.2904</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6188</v>
+        <v>3.7068</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7203</v>
+        <v>-0.4732</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.1015</v>
+        <v>4.1801</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8357</v>
+        <v>3.4049</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9779</v>
+        <v>-0.273</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.1422</v>
+        <v>3.6779</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.2169</v>
+        <v>0.3019</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2576</v>
+        <v>-0.2002</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9593</v>
+        <v>0.5021</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1586</v>
+        <v>-0.3859</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1116</v>
+        <v>-0.2424</v>
       </c>
       <c r="U2" t="n">
-        <v>0.047</v>
+        <v>-0.1435</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8645</v>
+        <v>-0.1168</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8574</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0071</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0266</v>
+        <v>4.4501</v>
       </c>
       <c r="E3" t="n">
-        <v>2.883</v>
+        <v>4.657</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1436</v>
+        <v>-0.2069</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7068</v>
+        <v>0.6188</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4732</v>
+        <v>2.7203</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1801</v>
+        <v>-2.1015</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4049</v>
+        <v>2.8357</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.273</v>
+        <v>3.9779</v>
       </c>
       <c r="L3" t="n">
-        <v>3.6779</v>
+        <v>-1.1422</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3019</v>
+        <v>-2.2169</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2002</v>
+        <v>-1.2576</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5021</v>
+        <v>-0.9593</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8122</v>
+        <v>1.5506</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5219</v>
+        <v>1.0045</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2903</v>
+        <v>0.5461</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1168</v>
+        <v>1.8645</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.8574</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1168</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5177</v>
+        <v>3.3378</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8023</v>
+        <v>2.9747</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7154</v>
+        <v>0.3631</v>
       </c>
       <c r="G4" t="n">
         <v>2.502</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0294</v>
+        <v>-0.1505</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6524</v>
+        <v>-0.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6818</v>
+        <v>0.3295</v>
       </c>
       <c r="V4" t="n">
         <v>-0.4706</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ORENGA IMAZ</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5274</v>
+        <v>1.8176</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7926</v>
+        <v>1.707</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2653</v>
+        <v>0.1106</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3409</v>
+        <v>-0.0187</v>
       </c>
       <c r="H5" t="n">
-        <v>0.243</v>
+        <v>-0.2261</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5839</v>
+        <v>0.2074</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3576</v>
+        <v>0.8265</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1617</v>
+        <v>0.8355</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1959</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6985</v>
+        <v>-0.8452</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9187</v>
+        <v>-1.0616</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7798</v>
+        <v>0.2164</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9038</v>
+        <v>0.8907</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2051</v>
+        <v>0.6506</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6988</v>
+        <v>0.2401</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2843</v>
+        <v>0.1132</v>
       </c>
       <c r="W5" t="n">
         <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5142</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6002</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7426</v>
+        <v>0.4976</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0949</v>
+        <v>0.1027</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0187</v>
+        <v>-0.5511</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2261</v>
+        <v>-0.4221</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2074</v>
+        <v>-0.129</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8265</v>
+        <v>0.6328</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8355</v>
+        <v>0.0148</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.618</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8452</v>
+        <v>-1.1839</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0616</v>
+        <v>-0.4369</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2164</v>
+        <v>-0.747</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2792</v>
+        <v>0.2275</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3138</v>
+        <v>-0.1352</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0346</v>
+        <v>0.3628</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1132</v>
+        <v>-0.1168</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-0.1168</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>P. ORENGA IMAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3668</v>
+        <v>0.1431</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1761</v>
+        <v>2.6139</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1907</v>
+        <v>-2.4708</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5511</v>
+        <v>-1.3409</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4221</v>
+        <v>0.243</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.129</v>
+        <v>-1.5839</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6328</v>
+        <v>1.3576</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0148</v>
+        <v>1.1617</v>
       </c>
       <c r="L7" t="n">
-        <v>0.618</v>
+        <v>0.1959</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1839</v>
+        <v>-2.6985</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4369</v>
+        <v>-0.9187</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.747</v>
+        <v>-1.7798</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0059</v>
+        <v>1.5196</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4567</v>
+        <v>1.0263</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4508</v>
+        <v>0.4932</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1168</v>
+        <v>-1.2843</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1168</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2635</v>
+        <v>-0.0893</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8639</v>
+        <v>-1.0805</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6003</v>
+        <v>0.9912</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8363</v>
+        <v>0.4381</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6101</v>
+        <v>1.3647</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2261</v>
+        <v>-0.9266</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6743</v>
+        <v>0.2258</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0221</v>
+        <v>0.9402</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6964</v>
+        <v>-0.7144</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5106</v>
+        <v>0.2122</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5881</v>
+        <v>0.4245</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9225</v>
+        <v>-0.2123</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0511</v>
+        <v>-0.3192</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9565</v>
+        <v>-0.2657</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0946</v>
+        <v>-0.0535</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9919</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2737</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.2655</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.364</v>
+        <v>-0.1996</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1038</v>
+        <v>0.5324</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4678</v>
+        <v>-0.732</v>
       </c>
       <c r="G9" t="n">
         <v>-2.214</v>
@@ -1156,13 +1156,13 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6317</v>
+        <v>1.7961</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7887</v>
+        <v>1.2173</v>
       </c>
       <c r="U9" t="n">
-        <v>0.843</v>
+        <v>0.5787</v>
       </c>
       <c r="V9" t="n">
         <v>1.0508</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5053</v>
+        <v>-0.2517</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4672</v>
+        <v>2.1138</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9618</v>
+        <v>-2.3655</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4381</v>
+        <v>-0.8363</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3647</v>
+        <v>-0.6101</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9266</v>
+        <v>-0.2261</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2258</v>
+        <v>0.6743</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9402</v>
+        <v>-0.0221</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7144</v>
+        <v>0.6964</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2122</v>
+        <v>-1.5106</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4245</v>
+        <v>-0.5881</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2123</v>
+        <v>-0.9225</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7353</v>
+        <v>1.5359</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6524</v>
+        <v>1.2064</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0828</v>
+        <v>0.3295</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.9919</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2737</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-3.2655</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2139</v>
+        <v>-1.7525</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.416</v>
+        <v>-0.1883</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2021</v>
+        <v>-1.5641</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4017</v>
+        <v>-1.1471</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1643</v>
+        <v>-1.5758</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7625</v>
+        <v>0.4286</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7444</v>
+        <v>-1.4287</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8619</v>
+        <v>-1.4287</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1176</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3426</v>
+        <v>0.2816</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3023</v>
+        <v>-0.147</v>
       </c>
       <c r="O11" t="n">
-        <v>0.645</v>
+        <v>0.4286</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8781</v>
+        <v>0.146</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4501</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.428</v>
+        <v>0.0731</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2335</v>
+        <v>-1.1675</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2335</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.963</v>
+        <v>-1.821</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.575</v>
+        <v>-3.9937</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.388</v>
+        <v>2.1728</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1471</v>
+        <v>-0.4017</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5758</v>
+        <v>-1.1643</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4286</v>
+        <v>0.7625</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4287</v>
+        <v>-0.7444</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4287</v>
+        <v>-0.8619</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.1176</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2816</v>
+        <v>0.3426</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.147</v>
+        <v>-0.3023</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4286</v>
+        <v>0.645</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4162</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0646</v>
+        <v>0.2711</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3138</v>
+        <v>-0.1276</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2492</v>
+        <v>0.3987</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1675</v>
+        <v>-0.2335</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3351</v>
+        <v>-0.2335</v>
       </c>
     </row>
     <row r="13">
@@ -1423,34 +1423,34 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.3617</v>
+        <v>10.6876</v>
       </c>
       <c r="E13" t="n">
-        <v>12.6703</v>
+        <v>12.9964</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3087</v>
+        <v>-2.3085</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7558999999999991</v>
+        <v>0.7558999999999996</v>
       </c>
       <c r="H13" t="n">
         <v>2.899</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.143100000000001</v>
+        <v>-2.1431</v>
       </c>
       <c r="J13" t="n">
-        <v>9.840499999999999</v>
+        <v>9.8405</v>
       </c>
       <c r="K13" t="n">
-        <v>8.269200000000001</v>
+        <v>8.2692</v>
       </c>
       <c r="L13" t="n">
         <v>1.5714</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.0847</v>
+        <v>-9.084700000000002</v>
       </c>
       <c r="N13" t="n">
         <v>-5.37</v>
@@ -1459,7 +1459,7 @@
         <v>-3.7146</v>
       </c>
       <c r="P13" t="n">
-        <v>5.2029</v>
+        <v>5.202899999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-8.3248</v>
@@ -1468,10 +1468,10 @@
         <v>13.5276</v>
       </c>
       <c r="S13" t="n">
-        <v>6.7555</v>
+        <v>7.081899999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>3.600999999999999</v>
+        <v>3.927099999999999</v>
       </c>
       <c r="U13" t="n">
         <v>3.1547</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5843</v>
+        <v>2.5408</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0869</v>
+        <v>4.1941</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5026</v>
+        <v>-1.6533</v>
       </c>
       <c r="G14" t="n">
         <v>2.5592</v>
@@ -1546,13 +1546,13 @@
         <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0373</v>
+        <v>-1.0809</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7177</v>
+        <v>-0.6105</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3196</v>
+        <v>-0.4703</v>
       </c>
       <c r="V14" t="n">
         <v>0.23</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LACUNZA ABECIA</t>
+          <t>P. ELSO GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3486</v>
+        <v>0.2529</v>
       </c>
       <c r="E15" t="n">
-        <v>0.48</v>
+        <v>0.0611</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1314</v>
+        <v>0.1918</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6759</v>
+        <v>0.1621</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.5927</v>
+        <v>0.1621</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9169</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2227</v>
+        <v>0.0192</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.1881</v>
+        <v>0.0192</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4108</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8985</v>
+        <v>0.1429</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4046</v>
+        <v>0.1429</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4939</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4189</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3295</v>
+        <v>0.0419</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7484</v>
+        <v>0.0489</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ELSO GONZALEZ</t>
+          <t>J. POTIER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1164</v>
+        <v>0.1988</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0461</v>
+        <v>2.0827</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1624</v>
+        <v>-1.8839</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1621</v>
+        <v>2.0517</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1621</v>
+        <v>2.2518</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0192</v>
+        <v>3.4278</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0192</v>
+        <v>3.2768</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1429</v>
+        <v>-1.3761</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1429</v>
+        <v>-1.025</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.351</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0457</v>
+        <v>-1.2743</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.6853</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0196</v>
+        <v>-0.5891</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.5026</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.2963</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2316</v>
+        <v>0.197</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3465</v>
+        <v>-0.4933</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4647</v>
@@ -1780,13 +1780,13 @@
         <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0698</v>
+        <v>0.212</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.261</v>
+        <v>0.1677</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1912</v>
+        <v>0.0444</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4599</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. POTIER</t>
+          <t>J. LACUNZA ABECIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7822</v>
+        <v>-0.3839</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3327</v>
+        <v>0.1585</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1149</v>
+        <v>-0.5424</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0517</v>
+        <v>-1.6759</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2518</v>
+        <v>-2.5927</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2</v>
+        <v>0.9169</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4278</v>
+        <v>0.2227</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2768</v>
+        <v>-1.1881</v>
       </c>
       <c r="L18" t="n">
-        <v>0.151</v>
+        <v>1.4108</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3761</v>
+        <v>-1.8985</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.025</v>
+        <v>-1.4046</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.351</v>
+        <v>-0.4939</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.9137</v>
+        <v>0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
         <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.2554</v>
+        <v>-0.3136</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4354</v>
+        <v>-0.651</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.82</v>
+        <v>0.3374</v>
       </c>
       <c r="V18" t="n">
-        <v>2.3351</v>
+        <v>1.3975</v>
       </c>
       <c r="W18" t="n">
-        <v>3.5026</v>
+        <v>1.6275</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2271</v>
+        <v>-0.7921</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8832</v>
+        <v>2.2047</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1103</v>
+        <v>-2.9968</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2905</v>
@@ -1936,13 +1936,13 @@
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2279</v>
+        <v>-1.793</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0439</v>
+        <v>-0.7224</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.184</v>
+        <v>-1.0705</v>
       </c>
       <c r="V19" t="n">
         <v>1.2914</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.855</v>
+        <v>-1.5448</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0675</v>
+        <v>0.8532</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9226</v>
+        <v>-2.398</v>
       </c>
       <c r="G20" t="n">
         <v>2.6648</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2306</v>
+        <v>-1.9203</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5252</v>
+        <v>-0.7396</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.7053</v>
+        <v>-1.1808</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0616</v>
+        <v>-2.499</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7451</v>
+        <v>-3.3881</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6836</v>
+        <v>0.8891</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8689</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8885</v>
+        <v>0.4511</v>
       </c>
       <c r="T21" t="n">
-        <v>0.972</v>
+        <v>0.3291</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0835</v>
+        <v>0.122</v>
       </c>
       <c r="V21" t="n">
         <v>1.1675</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4106</v>
+        <v>-2.5574</v>
       </c>
       <c r="E22" t="n">
         <v>-0.5387</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8719</v>
+        <v>-2.0187</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6019</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4736</v>
+        <v>-0.6204</v>
       </c>
       <c r="T22" t="n">
         <v>-0.46</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0136</v>
+        <v>-0.1604</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5838</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4963</v>
+        <v>-4.5663</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9804</v>
+        <v>-3.5162</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.516</v>
+        <v>-1.0501</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2918</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2772</v>
+        <v>0.2073</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7111</v>
+        <v>0.1753</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4338</v>
+        <v>0.032</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0249</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.3616</v>
+        <v>-9.647300000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3084</v>
+        <v>2.308299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.6702</v>
+        <v>-11.9556</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7558999999999998</v>
@@ -2299,7 +2299,7 @@
         <v>2.1431</v>
       </c>
       <c r="J24" t="n">
-        <v>9.084900000000001</v>
+        <v>9.084899999999998</v>
       </c>
       <c r="K24" t="n">
         <v>5.370200000000001</v>
@@ -2326,13 +2326,13 @@
         <v>8.3248</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.755700000000001</v>
+        <v>-6.0413</v>
       </c>
       <c r="T24" t="n">
         <v>-3.1548</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.6006</v>
+        <v>-2.8864</v>
       </c>
       <c r="V24" t="n">
         <v>2.3529</v>
